--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T09:58:03+00:00</t>
+    <t>2026-01-26T12:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T12:56:49+00:00</t>
+    <t>2026-02-05T13:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -634,7 +634,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date}
 </t>
   </si>
   <si>
@@ -654,7 +654,7 @@
     <t>TDDUIRessourcesUsed</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-ressources-used|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-ressources-used}
 </t>
   </si>
   <si>
@@ -737,7 +737,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-ressource-utilisee-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-ressource-utilisee-cisis</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -764,7 +764,7 @@
     <t>Encounter.extension:TDDUIRessourcesUsed.extension:TDDUIMaterialDetail.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-detail-materiel-specialise-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-detail-materiel-specialise-cisis</t>
   </si>
   <si>
     <t>Encounter.extension:TDDUIRessourcesUsed.extension:TDDUIFacilityResource</t>
@@ -785,7 +785,7 @@
     <t>Encounter.extension:TDDUIRessourcesUsed.extension:TDDUIFacilityResource.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-detail-ressource-immobiliere-utilisee-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-detail-ressource-immobiliere-utilisee-cisis</t>
   </si>
   <si>
     <t>Encounter.extension:TDDUIRessourcesUsed.url</t>
@@ -813,7 +813,7 @@
     <t>TDDUIEventLabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-label|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-label}
 </t>
   </si>
   <si>
@@ -829,7 +829,7 @@
     <t>TDDUIComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment}
 </t>
   </si>
   <si>
@@ -852,7 +852,7 @@
     <t>TDDUIEventReport</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-report|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-report}
 </t>
   </si>
   <si>
@@ -868,7 +868,7 @@
     <t>TDDUIAttachment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
@@ -887,7 +887,7 @@
     <t>TDDUIEventOutsideService</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-outside-service|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-outside-service}
 </t>
   </si>
   <si>
@@ -903,7 +903,7 @@
     <t>TDDUIEventReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-reason|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-reason}
 </t>
   </si>
   <si>
@@ -919,7 +919,7 @@
     <t>TDDUIPatientPresent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-present|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-present}
 </t>
   </si>
   <si>
@@ -935,7 +935,7 @@
     <t>TDDUIMeal</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-meal|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-meal}
 </t>
   </si>
   <si>
@@ -1037,7 +1037,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1126,7 +1126,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>TDDUIEventCancelReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-cancel-reason|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-event-cancel-reason}
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1468,7 +1468,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-type-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-type-vs</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:coding.system}
@@ -1574,7 +1574,7 @@
     <t>Encounter.type.coding.code</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-ssiad-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-ssiad-cisis</t>
   </si>
   <si>
     <t>Encounter.type:ssiad.coding.display</t>
@@ -1652,7 +1652,7 @@
     <t>Encounter.type:serafin.coding.code</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-serafin-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-serafin-valueset</t>
   </si>
   <si>
     <t>Encounter.type:serafin.coding.display</t>
@@ -1742,7 +1742,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1761,7 +1761,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot|Group|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|Group)
 </t>
   </si>
   <si>
@@ -1877,7 +1877,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant-vs</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1907,7 +1907,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|2.2.0-ballot|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|RelatedPerson)
 </t>
   </si>
   <si>
@@ -2009,7 +2009,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment)
 </t>
   </si>
   <si>
@@ -2352,7 +2352,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2398,7 +2398,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -2497,7 +2497,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -2536,7 +2536,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
@@ -2589,7 +2589,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -2604,7 +2604,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
 </t>
   </si>
   <si>
@@ -2626,7 +2626,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-sejour|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-sejour)
 </t>
   </si>
   <si>
@@ -2979,7 +2979,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="82.87890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.6640625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:38:35+00:00</t>
+    <t>2026-02-05T14:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:50:20+00:00</t>
+    <t>2026-02-05T15:15:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1203,7 +1203,7 @@
 </t>
   </si>
   <si>
-    <t>Évènement annulé</t>
+    <t>TDDUI Event Cancel Reason</t>
   </si>
   <si>
     <t>Motif associé au statut de non-réalisation de l’évènement.</t>
@@ -1468,7 +1468,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-type-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-type</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:coding.system}
@@ -1652,7 +1652,7 @@
     <t>Encounter.type:serafin.coding.code</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-serafin-valueset</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-serafin</t>
   </si>
   <si>
     <t>Encounter.type:serafin.coding.display</t>
@@ -1877,7 +1877,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1955,7 +1955,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/TDDUIEncounterParticipant"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-participant"/&gt;
     &lt;code value="AUT"/&gt;
     &lt;display value="Auteur du statut de la ressource"/&gt;
   &lt;/coding&gt;

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6949" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6949" uniqueCount="871">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -926,6 +926,10 @@
     <t>Evènement nécessitant ou non la présence physique de l’usager.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+- **Événement** : évènement nécessitant ou non la présence physique de l’usager.</t>
+  </si>
+  <si>
     <t>usagerPresent</t>
   </si>
   <si>
@@ -1903,7 +1907,9 @@
     <t>Indique la présence du participant lors de l'événement.</t>
   </si>
   <si>
-    <t>Indique la présence du participant à l'événement.</t>
+    <t>Indique la présence du participant à l'événement.
+- **Événement** :Indique la présence du participant à l'événement.
+- **Repas** : Indique la présence de l'usager au repas.</t>
   </si>
   <si>
     <t>Participant.presenceParticipant</t>
@@ -8212,7 +8218,7 @@
         <v>289</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8278,7 +8284,7 @@
         <v>120</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -8295,13 +8301,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>82</v>
@@ -8323,13 +8329,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8395,7 +8401,7 @@
         <v>120</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
@@ -8412,13 +8418,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -8440,13 +8446,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8512,7 +8518,7 @@
         <v>120</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
@@ -8529,10 +8535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8558,16 +8564,16 @@
         <v>112</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8616,7 +8622,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8648,10 +8654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8674,13 +8680,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8731,7 +8737,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8746,27 +8752,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8878,10 +8884,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8995,10 +9001,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9024,16 +9030,16 @@
         <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9061,10 +9067,10 @@
         <v>230</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -9082,7 +9088,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9103,7 +9109,7 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
@@ -9114,10 +9120,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9143,16 +9149,16 @@
         <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9181,7 +9187,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -9199,7 +9205,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9220,21 +9226,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9260,16 +9266,16 @@
         <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9279,10 +9285,10 @@
         <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -9318,7 +9324,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9339,21 +9345,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9379,13 +9385,13 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9399,7 +9405,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -9435,7 +9441,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9456,21 +9462,21 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9493,13 +9499,13 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9550,7 +9556,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9571,21 +9577,21 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9608,16 +9614,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9667,7 +9673,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9688,21 +9694,21 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9728,13 +9734,13 @@
         <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9763,10 +9769,10 @@
         <v>230</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9784,7 +9790,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -9799,27 +9805,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9845,10 +9851,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9931,10 +9937,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10044,13 +10050,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="B61" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="C61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
@@ -10072,13 +10078,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10144,7 +10150,7 @@
         <v>120</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -10161,13 +10167,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -10189,13 +10195,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10261,7 +10267,7 @@
         <v>120</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
@@ -10278,10 +10284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10307,10 +10313,10 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10361,7 +10367,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10393,10 +10399,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10419,16 +10425,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10478,7 +10484,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10510,10 +10516,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10625,10 +10631,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10742,14 +10748,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10771,16 +10777,16 @@
         <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10829,7 +10835,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10861,10 +10867,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10890,10 +10896,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10923,10 +10929,10 @@
         <v>230</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10944,7 +10950,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>91</v>
@@ -10976,10 +10982,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11002,13 +11008,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11059,7 +11065,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>91</v>
@@ -11091,10 +11097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11120,10 +11126,10 @@
         <v>146</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11153,10 +11159,10 @@
         <v>150</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11174,7 +11180,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -11195,21 +11201,21 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11321,10 +11327,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11438,10 +11444,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11467,16 +11473,16 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11525,7 +11531,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11546,21 +11552,21 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11586,13 +11592,13 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11642,7 +11648,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11663,21 +11669,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11703,14 +11709,14 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11759,7 +11765,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11780,21 +11786,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11820,14 +11826,14 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11876,7 +11882,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11897,21 +11903,21 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11934,19 +11940,19 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11995,7 +12001,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12016,21 +12022,21 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12053,13 +12059,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12110,7 +12116,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12142,10 +12148,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12257,10 +12263,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12374,14 +12380,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12403,16 +12409,16 @@
         <v>112</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12461,7 +12467,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12493,10 +12499,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12522,10 +12528,10 @@
         <v>146</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12555,10 +12561,10 @@
         <v>150</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12576,7 +12582,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>91</v>
@@ -12608,10 +12614,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12634,13 +12640,13 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12691,7 +12697,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>91</v>
@@ -12723,10 +12729,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12752,13 +12758,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12788,13 +12794,13 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12804,7 +12810,7 @@
         <v>118</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12819,30 +12825,30 @@
         <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12867,13 +12873,13 @@
         <v>227</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12902,10 +12908,10 @@
         <v>158</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12923,7 +12929,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12941,24 +12947,24 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13070,10 +13076,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13187,10 +13193,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13216,16 +13222,16 @@
         <v>146</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13274,7 +13280,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13295,21 +13301,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13421,10 +13427,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13538,10 +13544,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13567,16 +13573,16 @@
         <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13586,7 +13592,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -13625,7 +13631,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13646,21 +13652,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13686,13 +13692,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13742,7 +13748,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13763,21 +13769,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13803,14 +13809,14 @@
         <v>168</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13839,7 +13845,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13857,7 +13863,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13878,21 +13884,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13918,14 +13924,14 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13974,7 +13980,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13995,21 +14001,21 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14032,19 +14038,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14093,7 +14099,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14114,21 +14120,21 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14154,16 +14160,16 @@
         <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14212,7 +14218,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14233,24 +14239,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>82</v>
@@ -14275,13 +14281,13 @@
         <v>227</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14310,10 +14316,10 @@
         <v>158</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14331,7 +14337,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14349,24 +14355,24 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14478,10 +14484,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14595,10 +14601,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14624,16 +14630,16 @@
         <v>146</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14682,7 +14688,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14703,21 +14709,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14829,10 +14835,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14946,10 +14952,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14975,16 +14981,16 @@
         <v>134</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14994,7 +15000,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15033,7 +15039,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15054,21 +15060,21 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15094,13 +15100,13 @@
         <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15150,7 +15156,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15171,21 +15177,21 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15211,14 +15217,14 @@
         <v>168</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15247,7 +15253,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15265,7 +15271,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15286,21 +15292,21 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15326,14 +15332,14 @@
         <v>105</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15382,7 +15388,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15403,21 +15409,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15440,19 +15446,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15501,7 +15507,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15522,21 +15528,21 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15562,16 +15568,16 @@
         <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15620,7 +15626,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15641,24 +15647,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>82</v>
@@ -15683,13 +15689,13 @@
         <v>227</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15718,10 +15724,10 @@
         <v>158</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15739,7 +15745,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15757,24 +15763,24 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15886,10 +15892,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16003,10 +16009,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16032,16 +16038,16 @@
         <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16090,7 +16096,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16111,21 +16117,21 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16237,10 +16243,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16354,10 +16360,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16383,16 +16389,16 @@
         <v>134</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16402,7 +16408,7 @@
         <v>82</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>82</v>
@@ -16441,7 +16447,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16462,21 +16468,21 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16502,13 +16508,13 @@
         <v>105</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16558,7 +16564,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16579,21 +16585,21 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16619,14 +16625,14 @@
         <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16636,7 +16642,7 @@
         <v>82</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>82</v>
@@ -16675,7 +16681,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16696,21 +16702,21 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16736,14 +16742,14 @@
         <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16753,7 +16759,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -16792,7 +16798,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16813,21 +16819,21 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16850,19 +16856,19 @@
         <v>92</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16911,7 +16917,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16932,21 +16938,21 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16972,16 +16978,16 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17030,7 +17036,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17051,21 +17057,21 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17091,10 +17097,10 @@
         <v>227</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17124,10 +17130,10 @@
         <v>158</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17145,7 +17151,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17163,7 +17169,7 @@
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>109</v>
@@ -17172,15 +17178,15 @@
         <v>82</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17206,10 +17212,10 @@
         <v>227</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17239,10 +17245,10 @@
         <v>158</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -17260,7 +17266,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17281,25 +17287,25 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17318,16 +17324,16 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17377,7 +17383,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17392,27 +17398,27 @@
         <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17435,13 +17441,13 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17492,7 +17498,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17510,28 +17516,28 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17550,13 +17556,13 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17607,7 +17613,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17625,10 +17631,10 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17639,10 +17645,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17665,13 +17671,13 @@
         <v>92</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17722,7 +17728,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17740,24 +17746,24 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17869,10 +17875,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17982,13 +17988,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="B129" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="C129" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>82</v>
@@ -18010,13 +18016,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18082,7 +18088,7 @@
         <v>120</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18099,14 +18105,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18128,16 +18134,16 @@
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18186,7 +18192,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18218,10 +18224,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18247,13 +18253,13 @@
         <v>227</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18282,10 +18288,10 @@
         <v>150</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18303,7 +18309,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18321,24 +18327,24 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18361,13 +18367,13 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18418,7 +18424,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18439,21 +18445,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18476,13 +18482,13 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18533,7 +18539,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18548,27 +18554,27 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18591,13 +18597,13 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18648,7 +18654,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18666,24 +18672,24 @@
         <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18706,16 +18712,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18765,7 +18771,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18783,24 +18789,24 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18912,10 +18918,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19029,10 +19035,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19055,16 +19061,16 @@
         <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19114,7 +19120,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19123,33 +19129,33 @@
         <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19172,23 +19178,23 @@
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q139" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R139" t="s" s="2">
         <v>82</v>
@@ -19233,7 +19239,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19242,33 +19248,33 @@
         <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19291,16 +19297,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19350,7 +19356,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19368,28 +19374,28 @@
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19411,13 +19417,13 @@
         <v>227</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19446,10 +19452,10 @@
         <v>172</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19467,7 +19473,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19485,28 +19491,28 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19525,16 +19531,16 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19584,7 +19590,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19602,24 +19608,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19642,13 +19648,13 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19699,7 +19705,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19720,7 +19726,7 @@
         <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
@@ -19731,10 +19737,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19846,10 +19852,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19963,14 +19969,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19992,16 +19998,16 @@
         <v>112</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20050,7 +20056,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20082,14 +20088,14 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20108,16 +20114,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20167,7 +20173,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>91</v>
@@ -20185,24 +20191,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20228,10 +20234,10 @@
         <v>227</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20261,10 +20267,10 @@
         <v>172</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20282,7 +20288,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20314,10 +20320,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20340,13 +20346,13 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20397,7 +20403,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20418,7 +20424,7 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20429,10 +20435,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20455,16 +20461,16 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20514,7 +20520,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20535,7 +20541,7 @@
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20546,10 +20552,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20572,16 +20578,16 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20631,7 +20637,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20652,7 +20658,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20663,10 +20669,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20778,10 +20784,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20895,14 +20901,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20924,16 +20930,16 @@
         <v>112</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -20982,7 +20988,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21014,10 +21020,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21040,13 +21046,13 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21097,7 +21103,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21118,21 +21124,21 @@
         <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21244,10 +21250,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21361,10 +21367,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21390,16 +21396,16 @@
         <v>168</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -21427,10 +21433,10 @@
         <v>230</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>82</v>
@@ -21448,7 +21454,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21469,7 +21475,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21480,10 +21486,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21509,16 +21515,16 @@
         <v>227</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21547,7 +21553,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -21565,7 +21571,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21586,21 +21592,21 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21626,29 +21632,29 @@
         <v>134</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -21684,7 +21690,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21705,21 +21711,21 @@
         <v>82</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21745,13 +21751,13 @@
         <v>105</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21765,7 +21771,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -21801,7 +21807,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21822,21 +21828,21 @@
         <v>82</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21859,13 +21865,13 @@
         <v>92</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21916,7 +21922,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21937,21 +21943,21 @@
         <v>82</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21974,16 +21980,16 @@
         <v>92</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22033,7 +22039,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22054,21 +22060,21 @@
         <v>82</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22091,13 +22097,13 @@
         <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22148,7 +22154,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22169,7 +22175,7 @@
         <v>82</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>82</v>
@@ -22180,10 +22186,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22209,10 +22215,10 @@
         <v>227</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22242,10 +22248,10 @@
         <v>172</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22263,7 +22269,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22284,21 +22290,21 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22324,10 +22330,10 @@
         <v>227</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22357,10 +22363,10 @@
         <v>158</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22378,7 +22384,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22405,15 +22411,15 @@
         <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22439,16 +22445,16 @@
         <v>227</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22476,10 +22482,10 @@
         <v>158</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22497,7 +22503,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22518,21 +22524,21 @@
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22558,10 +22564,10 @@
         <v>227</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22591,10 +22597,10 @@
         <v>172</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22612,7 +22618,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22633,21 +22639,21 @@
         <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22673,10 +22679,10 @@
         <v>227</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22706,10 +22712,10 @@
         <v>172</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22727,7 +22733,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22748,21 +22754,21 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22785,13 +22791,13 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22842,7 +22848,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22863,21 +22869,21 @@
         <v>82</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22903,10 +22909,10 @@
         <v>227</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22937,7 +22943,7 @@
       </c>
       <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -22955,7 +22961,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22976,21 +22982,21 @@
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23013,16 +23019,16 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23072,7 +23078,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23087,13 +23093,13 @@
         <v>103</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>82</v>
@@ -23104,10 +23110,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23219,10 +23225,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23336,14 +23342,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23365,16 +23371,16 @@
         <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23423,7 +23429,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23455,10 +23461,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23481,13 +23487,13 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23538,7 +23544,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>91</v>
@@ -23556,24 +23562,24 @@
         <v>82</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23599,13 +23605,13 @@
         <v>168</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23634,10 +23640,10 @@
         <v>230</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>82</v>
@@ -23655,7 +23661,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23676,7 +23682,7 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>82</v>
@@ -23687,10 +23693,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23716,13 +23722,13 @@
         <v>227</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23752,7 +23758,7 @@
       </c>
       <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>82</v>
@@ -23770,7 +23776,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23802,10 +23808,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23828,13 +23834,13 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23885,7 +23891,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23906,7 +23912,7 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -23917,10 +23923,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23943,13 +23949,13 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -24000,7 +24006,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24015,27 +24021,27 @@
         <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24147,10 +24153,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24264,13 +24270,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="B183" t="s" s="2">
-        <v>835</v>
-      </c>
       <c r="C183" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D183" t="s" s="2">
         <v>82</v>
@@ -24292,13 +24298,13 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24364,7 +24370,7 @@
         <v>120</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>82</v>
@@ -24381,10 +24387,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24410,13 +24416,13 @@
         <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24466,7 +24472,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -24475,7 +24481,7 @@
         <v>91</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>103</v>
@@ -24498,10 +24504,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24527,13 +24533,13 @@
         <v>134</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24562,10 +24568,10 @@
         <v>150</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
@@ -24583,7 +24589,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24615,10 +24621,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24641,16 +24647,16 @@
         <v>92</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -24700,7 +24706,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24721,7 +24727,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24732,10 +24738,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24761,13 +24767,13 @@
         <v>105</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -24817,7 +24823,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -24849,10 +24855,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24875,16 +24881,16 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -24934,7 +24940,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24949,13 +24955,13 @@
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>82</v>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
